--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_27-07-2026.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_27-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Mannok_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934B09DD-C6E0-4C3A-85AA-1EAB1E1BC96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554F9EB4-1638-4F7D-9D0F-86F4441A495E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34185" yWindow="720" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33270" yWindow="3105" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -154,9 +154,6 @@
     <t>£40.20</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/90mm-mannok-pir-insulation-board-1200x2400mm/</t>
-  </si>
-  <si>
     <t>qt100mm</t>
   </si>
   <si>
@@ -236,6 +233,9 @@
   </si>
   <si>
     <t>£22.33</t>
+  </si>
+  <si>
+    <t>£40.15</t>
   </si>
 </sst>
 </file>
@@ -687,10 +687,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>11</v>
@@ -852,7 +852,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -863,22 +863,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
         <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>48</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
         <v>49</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>50</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -915,22 +915,22 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
         <v>53</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>54</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
         <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -941,10 +941,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
         <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -967,22 +967,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>60</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s">
         <v>61</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -993,22 +993,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
         <v>63</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
         <v>65</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1019,22 +1019,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
         <v>67</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>68</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
         <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" t="s">
-        <v>70</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
